--- a/template/7.7/量化业务日报-2025-07-07.xlsx
+++ b/template/7.7/量化业务日报-2025-07-07.xlsx
@@ -14,6 +14,7 @@
     <sheet name="量化三-结算数据" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="量化三-收盘数据" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="量化二持仓信息" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="量化二持仓信息--详细统计" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -153,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +218,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3472,7 +3475,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
       <c r="B6" s="20" t="n">
         <v>3.56</v>
       </c>
@@ -3579,8 +3586,10 @@
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
-        <v>6.0939</v>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>6.0939%</t>
+        </is>
       </c>
       <c r="C13" s="19" t="n"/>
       <c r="D13" s="19" t="n"/>
@@ -3592,7 +3601,7 @@
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>9830445.880000001</v>
+        <v>983.04</v>
       </c>
       <c r="C14" s="19" t="n"/>
       <c r="D14" s="19" t="n"/>
@@ -3604,7 +3613,7 @@
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>8888</v>
+        <v>0.89</v>
       </c>
       <c r="C15" s="19" t="n"/>
       <c r="D15" s="19" t="n"/>
@@ -3628,7 +3637,7 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>6880625</v>
+        <v>688.0599999999999</v>
       </c>
       <c r="C17" s="19" t="n"/>
       <c r="D17" s="19" t="n"/>
@@ -3640,7 +3649,7 @@
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>9999</v>
+        <v>1</v>
       </c>
       <c r="C18" s="19" t="n"/>
       <c r="D18" s="19" t="n"/>
@@ -3651,4 +3660,189 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>量化二持仓信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>统计日期</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>单位：万元</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>多头市值</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>空头市值</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>净市值</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>农副</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>有色</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>贵金属</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>股指期货</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>风险度：</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6.0939%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>权益：</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>983.04</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>当日盈亏：</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>总市值：</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>688.0599999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>去锁市值：</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>688.0599999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>平仓盈亏：</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/template/7.7/量化业务日报-2025-07-07.xlsx
+++ b/template/7.7/量化业务日报-2025-07-07.xlsx
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -218,8 +218,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2179,7 +2177,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>共持仓 37只期货， 持仓合约价值 688.06 万元, 其中空仓: 24 只,多仓: 13 只</t>
+          <t>共持仓 39只期货， 持仓合约价值 976.95 万元, 其中空仓: 25 只,多仓: 14 只</t>
         </is>
       </c>
       <c r="C31" s="17" t="n"/>
@@ -2557,7 +2555,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>共持仓 37只期货， 持仓合约价值 688.06 万元, 其中空仓: 24 只,多仓: 13 只</t>
+          <t>共持仓 39只期货， 持仓合约价值 976.95 万元, 其中空仓: 25 只,多仓: 14 只</t>
         </is>
       </c>
       <c r="C31" s="17" t="n"/>
@@ -3529,13 +3527,13 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>0</v>
+        <v>111.11</v>
       </c>
     </row>
     <row r="10">
@@ -3561,13 +3559,13 @@
         </is>
       </c>
       <c r="B11" s="20" t="n">
-        <v>229.1</v>
+        <v>429.1</v>
       </c>
       <c r="C11" s="21" t="n">
-        <v>458.96</v>
+        <v>547.85</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-229.86</v>
+        <v>-118.74</v>
       </c>
     </row>
     <row r="12">
@@ -3625,7 +3623,7 @@
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>688.0599999999999</v>
+        <v>976.95</v>
       </c>
       <c r="C16" s="19" t="n"/>
       <c r="D16" s="19" t="n"/>
@@ -3637,7 +3635,7 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>688.0599999999999</v>
+        <v>788.0599999999999</v>
       </c>
       <c r="C17" s="19" t="n"/>
       <c r="D17" s="19" t="n"/>
@@ -3668,181 +3666,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>量化二持仓信息</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>统计日期</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>2025-07-07</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>单位：万元</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>行业</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>多头市值</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>空头市值</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>净市值</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>农副</t>
         </is>
       </c>
+      <c r="B4" s="20" t="n">
+        <v>90.42</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>126.31</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>-35.89</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>豆油2509, 红枣2601, 菜籽油2509, 玉米淀粉2509, 玉米2509, 豆粕2509, 鲜鸡蛋2508, 豆一号2509, 白糖2509, 生猪2509, 棕榈油2509, 棉花2509, 苹果2510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>有色</t>
         </is>
       </c>
+      <c r="B5" s="20" t="n">
+        <v>106.62</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>锌2508, 铝2508, 氧化铝2509, 镍2508, 铅2508, 不锈钢2508, 铜2508</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>黑色</t>
         </is>
       </c>
+      <c r="B6" s="20" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>267.03</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>-263.47</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>玻璃2509, 甲醇N2509, 纯碱2509, PTA2509, 尿素2509, 乙二醇2509, 低硫燃料油2509, 聚乙烯2509, 聚氯乙烯2509, 苯乙烯2508, 天然橡胶2509, 聚丙烯2509, 石油沥青2509</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>黑色</t>
         </is>
       </c>
+      <c r="B7" s="20" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>38.88</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>硅铁2509, 锰硅2509, 焦煤2509, 热轧卷板2510, 焦炭2509, 螺纹钢2510, 铁矿石2509</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>贵金属</t>
         </is>
       </c>
+      <c r="B8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>-26.72</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>白银2508</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>股指期货</t>
         </is>
       </c>
+      <c r="B9" s="20" t="n">
+        <v>200</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>111.11</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IM001</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
+      <c r="B10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>-10.16</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>漂白硫酸盐针叶木浆2509</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
+      <c r="B11" s="20" t="n">
+        <v>429.1</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>547.85</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>-118.74</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>风险度：</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>6.0939%</t>
         </is>
       </c>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>权益：</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="19" t="n">
         <v>983.04</v>
       </c>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>当日盈亏：</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="19" t="n">
         <v>0.89</v>
       </c>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>总市值：</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>688.0599999999999</v>
-      </c>
+      <c r="B16" s="19" t="n">
+        <v>976.95</v>
+      </c>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>去锁市值：</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>688.0599999999999</v>
-      </c>
+      <c r="B17" s="19" t="n">
+        <v>788.0599999999999</v>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>平仓盈亏：</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="19" t="n">
         <v>1</v>
       </c>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>